--- a/docs/downloads/20260828_Seputeh Hills_Teduh Weekly Update.xlsx
+++ b/docs/downloads/20260828_Seputeh Hills_Teduh Weekly Update.xlsx
@@ -1012,7 +1012,7 @@
         <v/>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AA7" s="13">
         <f>Z7/$F$7</f>
@@ -1323,7 +1323,7 @@
         <v/>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AA10" s="13">
         <f>Z10/$F$10</f>
